--- a/BWI/bestwine_output/bestwine_India.xlsx
+++ b/BWI/bestwine_output/bestwine_India.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA115"/>
+  <dimension ref="A1:AA117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13304,6 +13304,184 @@
       <c r="Z115" s="2" t="inlineStr"/>
       <c r="AA115" s="2" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solis Group India </t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>168741</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Gurgaon</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>457, Pace City-II, Sector-37</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://solisgroup.in</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>contactus@solisgroup.in</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>+91 124 401 2704</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solis-group-india/</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/solisgroup.in</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solisgroup.in/</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Love K Jain</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/love-k-jain-20510613/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solis Group India </t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>168741</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Gurgaon</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>457, Pace City-II, Sector-37</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://solisgroup.in</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>contactus@solisgroup.in</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>+91 124 401 2704</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solis-group-india/</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/solisgroup.in</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solisgroup.in/</t>
+        </is>
+      </c>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>Anveeksha Tripathi</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>Operations &amp; Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anveeksha-tripathi-jain-26619920/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_India.xlsx
+++ b/BWI/bestwine_output/bestwine_India.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA117"/>
+  <dimension ref="A1:AA146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13482,6 +13482,2223 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Wine Palace Goa</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>168944</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Rudra Bhavan Kerant Caranzalem</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>403002</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://winepalacegoa.com</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>orders@winepalacegoa.com</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine.palace/</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr"/>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Alyona Private Limited</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>168940</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Besides Radisson Blu Hotel, SV Road, Goregaon West</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://alyonaindia.com/about-us</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>info@alyonaindia.com</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>Sarjak Bhojak</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarjak-bhojak-69317042/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Fine Bouche Beverages Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>168939</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>B-61, Kanakia Wall Street, A K Road, Chakala, Andheri East</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>400093</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://finebouche.in</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>pratikmehta876@gmail.com</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fine-bouche-beverages/</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>Pratik Mehta</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pratik-mehta-92626220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Sagar Wines Limited</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>168937</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>308, Ascot Centre, Next to Hotel Hilton, Off Sahar Road, Andheri East</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>400099</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://sagarwines.com</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>admin@sagarwines.in</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>+91 22 6916 7777</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr"/>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquors LLP</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>168936</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>6 Bajaj Park, Union Park, Khar West</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>400052</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.craftliquors.co.in</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Craftliquorsllp@gmail.com</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr"/>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Brewbulous Spirits Private Limited</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>168935</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>2nd Floor, Unit No. 202 SRS Tower, Sector 31</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>121003</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://brewbulous.com</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>hello@brewbulous.com</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brewbulous/</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/brewbuluos</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brewbulous/</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr"/>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Klassic Business Advisory Private Limited</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>168934</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>105, Plot No-65A, 1st Floor, Vijay Block, Laxmi Nagar</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>110092</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kbapl.com</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>care@kbapl.com</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Ajay Deewan</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ajay-deewan-3a3696289</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Klassic Business Advisory Private Limited</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>168934</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>105, Plot No-65A, 1st Floor, Vijay Block, Laxmi Nagar</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>110092</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kbapl.com</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>care@kbapl.com</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr"/>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Tomar</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/aditya-tomar-015801248</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>AI Logistics</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>168933</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Gurgaon</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>B-973 Palam Vihar</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>122017</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://ai-logistics.in</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>amitailogistic@gmail.com</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr"/>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>RootCrops</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>168932</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>C6, Phase 2, Sector 80</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>201305</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://root-crops.com</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>info@root-crops.com</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr"/>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rootcrops-trading-private-limited/</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Hoshiar Singh Kholia</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hoshiar-singh-kholia-4663251b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>RootCrops</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>168932</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>C6, Phase 2, Sector 80</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>201305</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://root-crops.com</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>info@root-crops.com</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rootcrops-trading-private-limited/</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Arpit Tandon</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>Sales Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arpit-tandon-aa62a6162/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITG Exim Private Limited </t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>International Trading Group</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>168931</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>8107, Ground Floor, DLF Phase IV</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>122002</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.itgexim.com</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>info@itgexim.com</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>+91 122 427 2099</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr"/>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr"/>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agways International </t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>House of Agways</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>168929</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>K-1102, AWHO-Mohali</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>140307</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://houseofagways.com</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>trade@houseofagways.com</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>+91 160 402 9398</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>D. S Kanwar</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>Chairman</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agways International </t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>House of Agways</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>168929</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>K-1102, AWHO-Mohali</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>140307</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://houseofagways.com</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>trade@houseofagways.com</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>+91 160 402 9398</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr"/>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>K. Jagmohan</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commercial Director </t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Winterfell Impex Private Limited</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>168928</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Trendz Park Plot No. 94, Gafoor nagar Village, Madhapur</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>500081</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winterfellimpex.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>contact@winterfell.co.in</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winterfell-impex/</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Aruna Kumari Mudunuri</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aruna-kumari-mudunuri-920797159/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Winterfell Impex Private Limited</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>168928</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Trendz Park Plot No. 94, Gafoor nagar Village, Madhapur</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>500081</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winterfellimpex.com</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>contact@winterfell.co.in</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr"/>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winterfell-impex/</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Raju Gunturi</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/v-v-s-n-raju-gunturi-72165b133</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Sony Group</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>168927</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>2245, Baliram Peth</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>425001</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://sonygroup.in/food-and-beverages</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>motoki.nakade@am.sony.com</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>+91 261 223 4440</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Takeshi Aimi</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, Business and Partner Development</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/takeshi-aimi-07417215</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Sony Group</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>168927</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2245, Baliram Peth</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>425001</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://sonygroup.in/food-and-beverages</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>motoki.nakade@am.sony.com</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+91 261 223 4440</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Motoki Nakade</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, Head of Business Development</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/motoki-nakade-94876b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Naktara Imports Private Limited</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>168926</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>No. 84, R. V. Road, Basavanagudi</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>560004</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.naktara.com</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>contact@naktara.com</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr"/>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Kambrell Overseas Private Limited</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>168925</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>7/16, First Floor, Left Side Office, Kirti Nagar Industrial Area</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>110015</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://kambrelloverseas.com</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>hello@kambrelloverseas.com</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>+91 11 4233 1643</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr"/>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/koplspirits</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>http://facebook.com/koplspirits</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/koplspirits</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr"/>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Penguin Overseas</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>168923</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>15/1, Rama Road</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>110015</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://penguinoverseas.com</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>gurjas@indoglobalgroup.net</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>+91 11 4507 8473</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/penguin-overseas/</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/penguin.overseas/</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/penguin.overseas/</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>Gurjas Singh</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gurjas-singh-754527269/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Bottle Bridge Beverages</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>168919</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>B/504, Basera CHSL., 3rd Cross Lane, Lokhandwala Market, Andheri West</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>400053</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bottle-bridge.com</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>info@bottle-bridge.com</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr"/>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bottle_bridge_beverages/</t>
+        </is>
+      </c>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr"/>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Cognac Brew Private Limited</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>168918</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Cuddalore</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>7/4, Muthukrishnan Street, Thirupapuliyur</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>607002</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://cognacbrew.com</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>info@cognacbrew.com</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr"/>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr"/>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>FBC Trades</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>168917</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Central Golf Link Rd, Golf Links</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>110003</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fbctrades.com</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>info@fbctrades.com</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr"/>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fbctrades/</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>Alex Yang</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>International Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexyang-fbctrades/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Suvira Spirits Private Limited</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>168916</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>A-17, 1st Floor, DDA Shed, Okhla Industrial Area, Phase-II</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>110020</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://suviraspirits.com</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>info@suviraspirits.co.in</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="R142" s="2" t="inlineStr"/>
+      <c r="S142" s="2" t="inlineStr"/>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sukhwinder Kaur</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Suvira Spirits Private Limited</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>168916</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>A-17, 1st Floor, DDA Shed, Okhla Industrial Area, Phase-II</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>110020</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://suviraspirits.com</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>info@suviraspirits.co.in</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>Gopal Joshi</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Suvira Spirits Private Limited</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>168916</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>A-17, 1st Floor, DDA Shed, Okhla Industrial Area, Phase-II</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>110020</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://suviraspirits.com</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>info@suviraspirits.co.in</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="2" t="inlineStr"/>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Kapil Bhagat</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Head</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Water Trading Private Limited</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>168915</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>103A, Block B, Ground Floor, Sushant Lok III, Sector 57</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>122011</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beyondwater.net</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>sales@beyondwater.in</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>+91 124 491 9795</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beyond-water-official/</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>Shubham Jha</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubham-jha-4aa893283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Water Trading Private Limited</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>168915</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>103A, Block B, Ground Floor, Sushant Lok III, Sector 57</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>122011</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beyondwater.net</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>sales@beyondwater.in</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>+91 124 491 9795</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beyond-water-official/</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr"/>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>Lakshhya Baid</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lakshhya-baid-08b8251b1/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
